--- a/Praktikum K-Means Manual/K Means Manual.xlsx
+++ b/Praktikum K-Means Manual/K Means Manual.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pendidikan\FOLDER IAN\Mata Kuliah AI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{820E47AD-230B-4B8C-B26C-CF20FFF6482D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DC1D4D4-DD69-4AC1-8DED-3E3FF8D844CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="K Means Manual" sheetId="1" r:id="rId1"/>
+    <sheet name="Silhouette Score" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="23">
   <si>
     <t>Cluster</t>
   </si>
@@ -86,6 +87,15 @@
   <si>
     <t>Centroid 2 (C2): C = (8,8)</t>
   </si>
+  <si>
+    <t>a(i)</t>
+  </si>
+  <si>
+    <t>b(i)</t>
+  </si>
+  <si>
+    <t>Silhouette Score</t>
+  </si>
 </sst>
 </file>
 
@@ -94,7 +104,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000_ "/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,6 +151,21 @@
       <name val="Calisto MT"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -150,7 +175,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -173,11 +198,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -200,6 +236,11 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -294,7 +335,7 @@
               <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:rPr>
-            <a:t>* Centroid 1 (C1): Hemat = (2, 2)</a:t>
+            <a:t>Centroid 1 (C1): Hemat = (2, 2)</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -303,7 +344,7 @@
               <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:rPr>
-            <a:t>* Centroid 2 (C2): Sultan = (8, 8)</a:t>
+            <a:t>Centroid 2 (C2): Sultan = (8, 8)</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -843,7 +884,7 @@
         <v>9.8994949366116654</v>
       </c>
       <c r="F2" s="9" t="str">
-        <f>IF(D2&lt;E2,"Hemat","Sultan")</f>
+        <f t="shared" ref="F2:F10" si="0">IF(D2&lt;E2,"Hemat","Sultan")</f>
         <v>Hemat</v>
       </c>
     </row>
@@ -866,7 +907,7 @@
         <v>9.2195444572928871</v>
       </c>
       <c r="F3" s="9" t="str">
-        <f>IF(D3&lt;E3,"Hemat","Sultan")</f>
+        <f t="shared" si="0"/>
         <v>Hemat</v>
       </c>
       <c r="H3" s="3" t="s">
@@ -884,15 +925,15 @@
         <v>3</v>
       </c>
       <c r="D4" s="4">
-        <f t="shared" ref="D2:D11" si="0">SQRT((B4-$K$5)^2+(C4-$L$5)^2)</f>
+        <f t="shared" ref="D4:D11" si="1">SQRT((B4-$K$5)^2+(C4-$L$5)^2)</f>
         <v>1.4142135623730951</v>
       </c>
       <c r="E4" s="4">
-        <f t="shared" ref="E2:E11" si="1">SQRT((B4-$K$6)^2+((C4-$L$6)^2))</f>
+        <f t="shared" ref="E4:E11" si="2">SQRT((B4-$K$6)^2+((C4-$L$6)^2))</f>
         <v>8.6023252670426267</v>
       </c>
       <c r="F4" s="9" t="str">
-        <f>IF(D4&lt;E4,"Hemat","Sultan")</f>
+        <f t="shared" si="0"/>
         <v>Hemat</v>
       </c>
     </row>
@@ -907,15 +948,15 @@
         <v>2</v>
       </c>
       <c r="D5" s="4">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="E5" s="4">
+        <f t="shared" si="2"/>
+        <v>7.810249675906654</v>
+      </c>
+      <c r="F5" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="E5" s="4">
-        <f t="shared" si="1"/>
-        <v>7.810249675906654</v>
-      </c>
-      <c r="F5" s="9" t="str">
-        <f>IF(D5&lt;E5,"Hemat","Sultan")</f>
         <v>Hemat</v>
       </c>
       <c r="H5" s="5" t="s">
@@ -939,15 +980,15 @@
         <v>4</v>
       </c>
       <c r="D6" s="4">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="E6" s="4">
+        <f t="shared" si="2"/>
+        <v>7.2111025509279782</v>
+      </c>
+      <c r="F6" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>2</v>
-      </c>
-      <c r="E6" s="4">
-        <f t="shared" si="1"/>
-        <v>7.2111025509279782</v>
-      </c>
-      <c r="F6" s="9" t="str">
-        <f>IF(D6&lt;E6,"Hemat","Sultan")</f>
         <v>Hemat</v>
       </c>
       <c r="H6" s="5" t="s">
@@ -971,15 +1012,15 @@
         <v>8</v>
       </c>
       <c r="D7" s="4">
+        <f t="shared" si="1"/>
+        <v>9.2195444572928871</v>
+      </c>
+      <c r="E7" s="4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F7" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>9.2195444572928871</v>
-      </c>
-      <c r="E7" s="4">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="F7" s="9" t="str">
-        <f>IF(D7&lt;E7,"Hemat","Sultan")</f>
         <v>Sultan</v>
       </c>
     </row>
@@ -994,15 +1035,15 @@
         <v>9</v>
       </c>
       <c r="D8" s="4">
+        <f t="shared" si="1"/>
+        <v>9.2195444572928871</v>
+      </c>
+      <c r="E8" s="4">
+        <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="F8" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>9.2195444572928871</v>
-      </c>
-      <c r="E8" s="4">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="F8" s="9" t="str">
-        <f>IF(D8&lt;E8,"Hemat","Sultan")</f>
         <v>Sultan</v>
       </c>
       <c r="H8" s="6"/>
@@ -1021,15 +1062,15 @@
         <v>7</v>
       </c>
       <c r="D9" s="4">
+        <f t="shared" si="1"/>
+        <v>7.0710678118654755</v>
+      </c>
+      <c r="E9" s="4">
+        <f t="shared" si="2"/>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="F9" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>7.0710678118654755</v>
-      </c>
-      <c r="E9" s="4">
-        <f t="shared" si="1"/>
-        <v>1.4142135623730951</v>
-      </c>
-      <c r="F9" s="9" t="str">
-        <f>IF(D9&lt;E9,"Hemat","Sultan")</f>
         <v>Sultan</v>
       </c>
       <c r="H9" s="7"/>
@@ -1048,15 +1089,15 @@
         <v>7</v>
       </c>
       <c r="D10" s="4">
+        <f t="shared" si="1"/>
+        <v>8.6023252670426267</v>
+      </c>
+      <c r="E10" s="4">
+        <f t="shared" si="2"/>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="F10" s="9" t="str">
         <f t="shared" si="0"/>
-        <v>8.6023252670426267</v>
-      </c>
-      <c r="E10" s="4">
-        <f t="shared" si="1"/>
-        <v>1.4142135623730951</v>
-      </c>
-      <c r="F10" s="9" t="str">
-        <f>IF(D10&lt;E10,"Hemat","Sultan")</f>
         <v>Sultan</v>
       </c>
       <c r="H10" s="2"/>
@@ -1075,11 +1116,11 @@
         <v>9</v>
       </c>
       <c r="D11" s="4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>10.63014581273465</v>
       </c>
       <c r="E11" s="4">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>2.2360679774997898</v>
       </c>
       <c r="F11" s="9" t="str">
@@ -2103,4 +2144,423 @@
   <pageSetup orientation="landscape"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA650950-F5E0-4E7A-8FAB-DE67CA12737D}">
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="8.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="26.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="15" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="3">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1</v>
+      </c>
+      <c r="D2" s="4">
+        <f>SQRT((B2-$L$5)^2+(C2-$M$5)^2)</f>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="E2" s="4">
+        <f>SQRT((B2-$L$6)^2+((C2-$M$6)^2))</f>
+        <v>9.8994949366116654</v>
+      </c>
+      <c r="F2" s="9" t="str">
+        <f t="shared" ref="F2:F10" si="0">IF(D2&lt;E2,"Hemat","Sultan")</f>
+        <v>Hemat</v>
+      </c>
+      <c r="G2" s="11">
+        <f>AVERAGE(SQRT(($B$2-$B$3)^2+($C$2-$C$3)^2), SQRT(($B$2-$B$4)^2+($C$2-$C$4)^2), SQRT(($B$2-$B$5)^2+($C$2-$C$5)^2), SQRT(($B$2-$B$6)^2+($C$2-$C$6)^2))</f>
+        <v>2.0995864094170424</v>
+      </c>
+      <c r="H2" s="5">
+        <f>AVERAGE(SQRT(($B$2-$B$7)^2+($C$2-$C$7)^2), SQRT(($B$2-$B$8)^2+($C$2-$C$8)^2), SQRT(($B$2-$B$9)^2+($C$2-$C$9)^2), SQRT(($B$2-$B$10)^2+($C$2-$C$10)^2), SQRT(($B$2-$B$11)^2+($C$2-$C$11)^2))</f>
+        <v>10.357433515700032</v>
+      </c>
+      <c r="I2" s="12">
+        <f>(H2-G2)/MAX(G2,H2)</f>
+        <v>0.79728700104765893</v>
+      </c>
+      <c r="K2" s="3"/>
+      <c r="L2" s="3"/>
+    </row>
+    <row r="3" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="3">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="4">
+        <f>SQRT((B3-$L$5)^2+(C3-$M$5)^2)</f>
+        <v>1</v>
+      </c>
+      <c r="E3" s="4">
+        <f>SQRT((B3-$L$6)^2+((C3-$M$6)^2))</f>
+        <v>9.2195444572928871</v>
+      </c>
+      <c r="F3" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Hemat</v>
+      </c>
+      <c r="G3" s="11">
+        <f>AVERAGE(SQRT(($B$3-$B$2)^2+($C$3-$C$2)^2), SQRT(($B$3-$B$4)^2+($C$3-$C$4)^2), SQRT(($B$3-$B$5)^2+($C$3-$C$5)^2), SQRT(($B$3-$B$6)^2+($C$3-$C$6)^2))</f>
+        <v>1.9125703849682212</v>
+      </c>
+      <c r="H3" s="5">
+        <f>AVERAGE(SQRT(($B$3-$B$7)^2+($C$3-$C$7)^2), SQRT(($B$3-$B$8)^2+($C$3-$C$8)^2), SQRT(($B$3-$B$9)^2+($C$3-$C$9)^2), SQRT(($B$3-$B$10)^2+($C$3-$C$10)^2), SQRT(($B$3-$B$11)^2+($C$3-$C$11)^2))</f>
+        <v>9.6485995137591924</v>
+      </c>
+      <c r="I3" s="12">
+        <f>(H3-G3)/MAX(G3,H3)</f>
+        <v>0.80177741005408731</v>
+      </c>
+      <c r="K3" s="3"/>
+      <c r="L3" s="3"/>
+    </row>
+    <row r="4" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3">
+        <v>3</v>
+      </c>
+      <c r="D4" s="4">
+        <f>SQRT((B4-$L$5)^2+(C4-$M$5)^2)</f>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="E4" s="4">
+        <f>SQRT((B4-$L$6)^2+((C4-$M$6)^2))</f>
+        <v>8.6023252670426267</v>
+      </c>
+      <c r="F4" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Hemat</v>
+      </c>
+      <c r="G4" s="11">
+        <f>AVERAGE(SQRT(($B$4-$B$2)^2+($C$4-$C$2)^2), SQRT(($B$4-$B$3)^2+($C$4-$C$3)^2), SQRT(($B$4-$B$5)^2+($C$4-$C$5)^2), SQRT(($B$4-$B$6)^2+($C$4-$C$6)^2))</f>
+        <v>1.9715873793431686</v>
+      </c>
+      <c r="H4" s="5">
+        <f>AVERAGE(SQRT(($B$4-$B$7)^2+($C$4-$C$7)^2), SQRT(($B$4-$B$8)^2+($C$4-$C$8)^2), SQRT(($B$4-$B$9)^2+($C$4-$C$9)^2), SQRT(($B$4-$B$10)^2+($C$4-$C$10)^2), SQRT(($B$4-$B$11)^2+($C$4-$C$11)^2))</f>
+        <v>9.1251107753337202</v>
+      </c>
+      <c r="I4" s="12">
+        <f>(H4-G4)/MAX(G4,H4)</f>
+        <v>0.78393825259934291</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="3">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3">
+        <v>2</v>
+      </c>
+      <c r="D5" s="4">
+        <f>SQRT((B5-$L$5)^2+(C5-$M$5)^2)</f>
+        <v>1</v>
+      </c>
+      <c r="E5" s="4">
+        <f>SQRT((B5-$L$6)^2+((C5-$M$6)^2))</f>
+        <v>7.810249675906654</v>
+      </c>
+      <c r="F5" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Hemat</v>
+      </c>
+      <c r="G5" s="11">
+        <f>AVERAGE(SQRT(($B$5-$B$2)^2+($C$5-$C$2)^2), SQRT(($B$5-$B$3)^2+($C$5-$C$3)^2), SQRT(($B$5-$B$4)^2+($C$5-$C$4)^2), SQRT(($B$5-$B$6)^2+($C$5-$C$6)^2))</f>
+        <v>2.0306043737181163</v>
+      </c>
+      <c r="H5" s="5">
+        <f>AVERAGE(SQRT(($B$5-$B$7)^2+($C$5-$C$7)^2), SQRT(($B$5-$B$8)^2+($C$5-$C$8)^2), SQRT(($B$5-$B$9)^2+($C$5-$C$9)^2), SQRT(($B$5-$B$10)^2+($C$5-$C$10)^2), SQRT(($B$5-$B$11)^2+($C$5-$C$11)^2))</f>
+        <v>8.2400950982464742</v>
+      </c>
+      <c r="I5" s="12">
+        <f>(H5-G5)/MAX(G5,H5)</f>
+        <v>0.75357027443163405</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="L5" s="3">
+        <v>2</v>
+      </c>
+      <c r="M5" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2</v>
+      </c>
+      <c r="C6" s="3">
+        <v>4</v>
+      </c>
+      <c r="D6" s="4">
+        <f>SQRT((B6-$L$5)^2+(C6-$M$5)^2)</f>
+        <v>2</v>
+      </c>
+      <c r="E6" s="4">
+        <f>SQRT((B6-$L$6)^2+((C6-$M$6)^2))</f>
+        <v>7.2111025509279782</v>
+      </c>
+      <c r="F6" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Hemat</v>
+      </c>
+      <c r="G6" s="11">
+        <f>AVERAGE(SQRT(($B$6-$B$2)^2+($C$6-$C$2)^2), SQRT(($B$6-$B$3)^2+($C$6-$C$3)^2), SQRT(($B$6-$B$4)^2+($C$6-$C$4)^2), SQRT(($B$6-$B$5)^2+($C$6-$C$5)^2))</f>
+        <v>2.453139800010316</v>
+      </c>
+      <c r="H6" s="5">
+        <f>AVERAGE(SQRT(($B$6-$B$7)^2+($C$6-$C$7)^2), SQRT(($B$6-$B$8)^2+($C$6-$C$8)^2), SQRT(($B$6-$B$9)^2+($C$6-$C$9)^2), SQRT(($B$6-$B$10)^2+($C$6-$C$10)^2), SQRT(($B$6-$B$11)^2+($C$6-$C$11)^2))</f>
+        <v>7.7506427113942022</v>
+      </c>
+      <c r="I6" s="12">
+        <f>(H6-G6)/MAX(G6,H6)</f>
+        <v>0.68349208041754261</v>
+      </c>
+      <c r="K6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="L6" s="3">
+        <v>8</v>
+      </c>
+      <c r="M6" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="3">
+        <v>9</v>
+      </c>
+      <c r="C7" s="3">
+        <v>8</v>
+      </c>
+      <c r="D7" s="4">
+        <f>SQRT((B7-$L$5)^2+(C7-$M$5)^2)</f>
+        <v>9.2195444572928871</v>
+      </c>
+      <c r="E7" s="4">
+        <f>SQRT((B7-$L$6)^2+((C7-$M$6)^2))</f>
+        <v>1</v>
+      </c>
+      <c r="F7" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Sultan</v>
+      </c>
+      <c r="G7" s="11">
+        <f>AVERAGE(SQRT(($B$7-$B$8)^2+($C$7-$C$8)^2), SQRT(($B$7-$B$9)^2+($C$7-$C$9)^2), SQRT(($B$7-$B$10)^2+($C$7-$C$10)^2), SQRT(($B$7-$B$11)^2+($C$7-$C$11)^2))</f>
+        <v>1.5161237755614949</v>
+      </c>
+      <c r="H7" s="5">
+        <f>AVERAGE(SQRT(($B$7-$B$2)^2+($C$7-$C$2)^2), SQRT(($B$7-$B$3)^2+($C$7-$C$3)^2), SQRT(($B$7-$B$4)^2+($C$7-$C$4)^2), SQRT(($B$7-$B$5)^2+($C$7-$C$5)^2), SQRT(($B$7-$B$6)^2+($C$7-$C$6)^2))</f>
+        <v>9.3022322007880067</v>
+      </c>
+      <c r="I7" s="12">
+        <f>(H7-G7)/MAX(G7,H7)</f>
+        <v>0.83701505801660581</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+      <c r="C8">
+        <v>9</v>
+      </c>
+      <c r="D8" s="4">
+        <f>SQRT((B8-$L$5)^2+(C8-$M$5)^2)</f>
+        <v>9.2195444572928871</v>
+      </c>
+      <c r="E8" s="4">
+        <f>SQRT((B8-$L$6)^2+((C8-$M$6)^2))</f>
+        <v>1</v>
+      </c>
+      <c r="F8" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Sultan</v>
+      </c>
+      <c r="G8" s="11">
+        <f>AVERAGE(SQRT(($B$8-$B$7)^2+($C$8-$C$7)^2), SQRT(($B$8-$B$9)^2+($C$8-$C$9)^2), SQRT(($B$8-$B$10)^2+($C$8-$C$10)^2), SQRT(($B$8-$B$11)^2+($C$8-$C$11)^2))</f>
+        <v>1.9715873793431686</v>
+      </c>
+      <c r="H8" s="5">
+        <f>AVERAGE(SQRT(($B$8-$B$2)^2+($C$8-$C$2)^2), SQRT(($B$8-$B$3)^2+($C$8-$C$3)^2), SQRT(($B$8-$B$4)^2+($C$8-$C$4)^2), SQRT(($B$8-$B$5)^2+($C$8-$C$5)^2), SQRT(($B$8-$B$6)^2+($C$8-$C$6)^2))</f>
+        <v>9.2524530425953646</v>
+      </c>
+      <c r="I8" s="12">
+        <f>(H8-G8)/MAX(G8,H8)</f>
+        <v>0.78691192808365473</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9">
+        <v>7</v>
+      </c>
+      <c r="C9">
+        <v>7</v>
+      </c>
+      <c r="D9" s="4">
+        <f>SQRT((B9-$L$5)^2+(C9-$M$5)^2)</f>
+        <v>7.0710678118654755</v>
+      </c>
+      <c r="E9" s="4">
+        <f>SQRT((B9-$L$6)^2+((C9-$M$6)^2))</f>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="F9" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Sultan</v>
+      </c>
+      <c r="G9" s="11">
+        <f>AVERAGE(SQRT(($B$9-$B$7)^2+($C$9-$C$7)^2), SQRT(($B$9-$B$8)^2+($C$9-$C$8)^2), SQRT(($B$9-$B$10)^2+($C$9-$C$10)^2), SQRT(($B$9-$B$11)^2+($C$9-$C$11)^2))</f>
+        <v>2.5194218076158923</v>
+      </c>
+      <c r="H9" s="5">
+        <f>AVERAGE(SQRT(($B$9-$B$2)^2+($C$9-$C$2)^2), SQRT(($B$9-$B$3)^2+($C$9-$C$3)^2), SQRT(($B$9-$B$4)^2+($C$9-$C$4)^2), SQRT(($B$9-$B$5)^2+($C$9-$C$5)^2), SQRT(($B$9-$B$6)^2+($C$9-$C$6)^2))</f>
+        <v>7.14814194667027</v>
+      </c>
+      <c r="I9" s="12">
+        <f>(H9-G9)/MAX(G9,H9)</f>
+        <v>0.64754172113363206</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+      <c r="D10" s="4">
+        <f>SQRT((B10-$L$5)^2+(C10-$M$5)^2)</f>
+        <v>8.6023252670426267</v>
+      </c>
+      <c r="E10" s="4">
+        <f>SQRT((B10-$L$6)^2+((C10-$M$6)^2))</f>
+        <v>1.4142135623730951</v>
+      </c>
+      <c r="F10" s="9" t="str">
+        <f t="shared" si="0"/>
+        <v>Sultan</v>
+      </c>
+      <c r="G10" s="11">
+        <f>AVERAGE(SQRT(($B$10-$B$7)^2+($C$10-$C$7)^2), SQRT(($B$10-$B$8)^2+($C$10-$C$8)^2), SQRT(($B$10-$B$9)^2+($C$10-$C$9)^2), SQRT(($B$10-$B$11)^2+($C$10-$C$11)^2))</f>
+        <v>1.8680339887498949</v>
+      </c>
+      <c r="H10" s="5">
+        <f>AVERAGE(SQRT(($B$10-$B$2)^2+($C$10-$C$2)^2), SQRT(($B$10-$B$3)^2+($C$10-$C$3)^2), SQRT(($B$10-$B$4)^2+($C$10-$C$4)^2), SQRT(($B$10-$B$5)^2+($C$10-$C$5)^2), SQRT(($B$10-$B$6)^2+($C$10-$C$6)^2))</f>
+        <v>8.7179678298125225</v>
+      </c>
+      <c r="I10" s="12">
+        <f>(H10-G10)/MAX(G10,H10)</f>
+        <v>0.78572598279591654</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11">
+        <v>9</v>
+      </c>
+      <c r="D11" s="4">
+        <f>SQRT((B11-$L$5)^2+(C11-$M$5)^2)</f>
+        <v>10.63014581273465</v>
+      </c>
+      <c r="E11" s="4">
+        <f>SQRT((B11-$L$6)^2+((C11-$M$6)^2))</f>
+        <v>2.2360679774997898</v>
+      </c>
+      <c r="F11" s="9" t="str">
+        <f>IF(D2&lt;E2,"Hemat","Sultan")</f>
+        <v>Hemat</v>
+      </c>
+      <c r="G11" s="11">
+        <f>AVERAGE(SQRT(($B$11-$B$2)^2+($C$11-$C$2)^2), SQRT(($B$11-$B$3)^2+($C$11-$C$3)^2), SQRT(($B$11-$B$4)^2+($C$11-$C$4)^2), SQRT(($B$11-$B$5)^2+($C$11-$C$5)^2), SQRT(($B$11-$B$6)^2+($C$11-$C$6)^2))</f>
+        <v>10.70108659456746</v>
+      </c>
+      <c r="H11" s="5">
+        <f>AVERAGE(SQRT(($B$11-$B$7)^2+($C$11-$C$7)^2), SQRT(($B$11-$B$8)^2+($C$11-$C$8)^2), SQRT(($B$11-$B$9)^2+($C$11-$C$9)^2), SQRT(($B$11-$B$10)^2+($C$11-$C$10)^2))</f>
+        <v>2.3139582038342184</v>
+      </c>
+      <c r="I11" s="12">
+        <f>(H11-G11)/MAX(G11,H11)</f>
+        <v>-0.78376418288130401</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>